--- a/data/file_generation/reference/data_60/1_res.xlsx
+++ b/data/file_generation/reference/data_60/1_res.xlsx
@@ -2104,26 +2104,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58C3CB7D-AD95-4B6C-A462-D925C1AEE0B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A80E333A-B73E-4833-AD3B-5519A063B5FE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA507266-369B-4609-A8B1-069D0119384A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8514F991-0696-422B-B26D-BC3516CEF079}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AB971CE-5560-44F9-9851-6D6241238025}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04575EEE-72CD-476D-B57D-9E47027F154C}"/>
 </file>